--- a/ExpLogs/251202_1015/Update_Result.xlsx
+++ b/ExpLogs/251202_1015/Update_Result.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yuu53\Projects\Research_Master\force_plate\ExpLogs\251202_1015\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B83A754-6A11-47B2-8B15-58E918179BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C02867-1DAA-46D5-BE58-E41D50A100D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{2438DD00-2094-44D1-800B-5E5E3A4374CD}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>平面着地衝撃力</t>
     <rPh sb="0" eb="4">
@@ -162,6 +162,32 @@
     </rPh>
     <rPh sb="78" eb="80">
       <t>チュウイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Average</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Median</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Standard Seviation</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Minimum</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーバー用</t>
+    <rPh sb="5" eb="6">
+      <t>ヨウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -534,7 +560,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -635,6 +661,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -652,6 +681,1313 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ja-JP"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>flat foot contact</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$B$24:$B$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$B$24:$B$25,Sheet1!$B$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.68702256149271201</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$B$24:$B$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$B$24:$B$25,Sheet1!$B$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.68702256149271201</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$A$15:$A$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$A$15:$A$16,Sheet1!$A$18:$A$19)</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Median</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Maximum</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Minimum</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$B$15:$B$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$B$15:$B$16,Sheet1!$B$18:$B$19)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>8.1999999999999993</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>5.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CE45-4899-A492-0832F81D82D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>heel strike (heel contact)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$E$24:$E$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$E$24:$E$25,Sheet1!$E$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.34655446902327064</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$E$24:$E$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$E$24:$E$25,Sheet1!$E$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.34655446902327064</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$A$15:$A$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$A$15:$A$16,Sheet1!$A$18:$A$19)</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Median</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Maximum</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Minimum</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$E$15:$E$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$E$15:$E$16,Sheet1!$E$18:$E$19)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.7299999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.8</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>1.9</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-CE45-4899-A492-0832F81D82D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>heel strike (sole contact)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:errBars>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$F$24:$F$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$F$24:$F$25,Sheet1!$F$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.33481338085566298</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:extLst>
+                  <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                    <c15:fullRef>
+                      <c15:sqref>Sheet1!$F$24:$F$27</c15:sqref>
+                    </c15:fullRef>
+                  </c:ext>
+                </c:extLst>
+                <c:f>(Sheet1!$F$24:$F$25,Sheet1!$F$27)</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="3"/>
+                  <c:pt idx="0">
+                    <c:v>0.33481338085566298</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$A$15:$A$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$A$15:$A$16,Sheet1!$A$18:$A$19)</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Median</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Maximum</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Minimum</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Sheet1!$F$15:$F$19</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>(Sheet1!$F$15:$F$16,Sheet1!$F$18:$F$19)</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.5300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>3.1</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>2.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-CE45-4899-A492-0832F81D82D1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1421810912"/>
+        <c:axId val="1421809472"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1421810912"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1421809472"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1421809472"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="9"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>impact force[N]</a:t>
+                </a:r>
+                <a:endParaRPr lang="ja-JP"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ja-JP"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1421810912"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="ja-JP"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>643890</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="グラフ 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18301E6D-BE1D-47C3-9FA7-7957E5707EF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -971,7 +2307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3A555C-5D63-4691-8849-6A1640474937}">
-  <dimension ref="A2:H21"/>
+  <dimension ref="A2:H27"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="13.19921875" bestFit="1" customWidth="1"/>
@@ -1209,7 +2545,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="23" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B15" s="16">
         <f>AVERAGE($B$5:$B$14)</f>
@@ -1236,7 +2572,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="24" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B16" s="17">
         <f>MEDIAN($B$5:$B$14)</f>
@@ -1263,7 +2599,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="24" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B17" s="17">
         <f>_xlfn.STDEV.P($B$5:$B$14)</f>
@@ -1290,7 +2626,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="24" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B18" s="14">
         <f>MAX(B$5:B$14)</f>
@@ -1317,7 +2653,7 @@
     </row>
     <row r="19" spans="1:8" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A19" s="25" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B19" s="15">
         <f>MIN(B$5:B$14)</f>
@@ -1347,8 +2683,61 @@
         <v>10</v>
       </c>
     </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B24" s="34">
+        <f>$B$17</f>
+        <v>0.68702256149271201</v>
+      </c>
+      <c r="E24" s="34">
+        <f>$E$17</f>
+        <v>0.34655446902327064</v>
+      </c>
+      <c r="F24" s="34">
+        <f>$F$17</f>
+        <v>0.33481338085566298</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>